--- a/artfynd/A 62632-2022 artfynd.xlsx
+++ b/artfynd/A 62632-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62632-2022 artfynd.xlsx
+++ b/artfynd/A 62632-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>105314876</v>
       </c>
       <c r="B2" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605509.3399241481</v>
+        <v>605509</v>
       </c>
       <c r="R2" t="n">
-        <v>7064800.362954535</v>
+        <v>7064800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105310256</v>
+        <v>105314874</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605408.0385291879</v>
+        <v>605492</v>
       </c>
       <c r="R3" t="n">
-        <v>7064825.83294671</v>
+        <v>7064879</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105314874</v>
+        <v>105314877</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>605492.052359499</v>
+        <v>605512</v>
       </c>
       <c r="R4" t="n">
-        <v>7064878.796527419</v>
+        <v>7064803</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +947,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105314877</v>
+        <v>105310256</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605511.9149267536</v>
+        <v>605408</v>
       </c>
       <c r="R5" t="n">
-        <v>7064803.112305433</v>
+        <v>7064826</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,19 +1049,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 62632-2022 artfynd.xlsx
+++ b/artfynd/A 62632-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105314877</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>